--- a/docs/test/コレクレ_発送・サロン予約フロー_シナリオテスト.xlsx
+++ b/docs/test/コレクレ_発送・サロン予約フロー_シナリオテスト.xlsx
@@ -99,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -122,6 +122,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:A52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -496,7 +497,7 @@
     <row r="1" ht="20.25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>コレクレ 発送・サロン予約フロー 差分確認シナリオテスト</t>
+          <t>コレクレ 発送・サロン予約フロー ほか 差分確認シナリオテスト</t>
         </is>
       </c>
     </row>
@@ -528,240 +529,300 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="3" t="n"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="6" ht="57" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>追加の変更（⑩〜⑭）: 運用者から提携企業への一斉メール（宛先のユーザーごとの選択を含む）、導入企業の請求情報（月額基本料の追加、運用者の「請求管理」画面、管理者の「請求情報」タブ、収支ダッシュボードの収入計算）、提携企業向けの操作ガイド（/docs）、管理者の会社情報まわりのセキュリティ修正と運用者の収支ダッシュボードのログイン必須化、本番ビルド時の必須環境変数チェックと CI。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>【テストを始める前の状態】</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>・stage 環境の 提携企業／従業員／運用者 のテストアカウントでログインできる</t>
         </is>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>・各アカウントの通知メールを受信・確認できる</t>
+          <t>・stage 環境の 提携企業／従業員／管理者（導入企業）／運用者 のテストアカウントでログインできる</t>
         </is>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>・各アカウントの通知メールを受信・確認できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
           <t>・従業員アカウントに交換申請できるだけのポイントがある（不足時は管理者のポイント調整で付与）</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="28.5" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12" ht="28.5" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>・順番の目安: ①発送型の商品を用意 → ②従業員が交換申請 → ③お届け日を確定 → ④発送情報を入れて発送済みに → ⑤申請者が受け取り確認、の流れで進めると自然につながります。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="3" t="n"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="13"/>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>【テストの進め方】</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>1. 「シナリオ一覧」のシートを開きます。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2. 上から順番に、書いてある手順どおりに操作してください。</t>
+          <t>1. 「シナリオ一覧」のシートを開きます。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>3. 「期待する結果」と実際の画面を見比べて、合っていれば「結果」欄に「OK」と書いてください。</t>
+          <t>2. 上から順番に、書いてある手順どおりに操作してください。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>4. 違っていたら「NG」と書き、「気づいたこと・スクショ」欄に状況を書いてください。</t>
+          <t>3. 「期待する結果」と実際の画面を見比べて、合っていれば「結果」欄に「OK」と書いてください。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   （できれば画面のスクリーンショットを撮ってください）</t>
+          <t>4. 違っていたら「NG」と書き、「気づいたこと・スクショ」欄に状況を書いてください。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>5. 実施できない・対象外の場合は「-」と書いてください。</t>
+          <t xml:space="preserve">   （できれば画面のスクリーンショットを撮ってください）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>5. 実施できない・対象外の場合は「-」と書いてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   （⑦の日次バッチは、時間経過やバッチ実行が必要なため「-」でも構いません）</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="28.5" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="22" ht="28.5" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">   （⑨のホットペッパービューティーの画面確認では、予約を確定させないでください。日時選択の画面まで進んだら戻って構いません）</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="3" t="n"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>【事前に用意するもの】</t>
+    <row r="23" ht="28.5" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   （⑩の一斉メールは、本当にメールが送られます。本送信は、自分で受け取れるアドレスだけを登録したテスト用の提携企業を選んで行ってください。実在の提携企業には送らないでください）</t>
         </is>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>・発送型で「お届け日の調整あり」の商品（冷蔵・冷凍など）</t>
+          <t xml:space="preserve">   （⑪で月額基本料・月額単価・企業のステータスを変えた場合は、テストが終わったら元の値に戻してください）</t>
         </is>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   （⑭は開発者向けの確認です。テスト担当の方は「-」で構いません）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>【事前に用意するもの】</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="14.25" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>・発送型で「お届け日の調整あり」の商品（冷蔵・冷凍など）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="14.25" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
           <t>・発送型で「お届け日の調整なし」の商品（従来フローの確認用）</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="30" ht="14.25" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>・来店受取または予約型サービスの商品（発送情報が出ないことの確認用）</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="28.5" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="31" ht="28.5" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>・予約型サービスの商品を2つ（予約に使っているサービスが「ホットペッパービューティー」のものと「その他」のもの。⑨で作成します）</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="28.5" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="32" ht="14.25" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>・ホットペッパービューティーのサロンのトップページURL（例: https://beauty.hotpepper.jp/slnH000000000/ の形）</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="28.5" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="33" ht="14.25" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>・ヤマト運輸・佐川急便・日本郵便の送り状番号（実在のものでなくて構いませんが、桁数は12桁程度にしてください）</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="3" t="n"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="34" ht="28.5" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>・一斉メール用のテスト提携企業を2社（それぞれ、自分が受け取れるメールアドレスのユーザーか連絡先を登録しておく。Gmail の「+」付きアドレスなどで分けると確認しやすいです。⑩で使います）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="14.25" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>・請求確認用の導入企業（運用者の企業登録で、月額基本料・月額単価・有効ユーザー数を控えておく。⑪で使います）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="14.25" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>・ログインしていない状態のブラウザ（シークレットウィンドウ。⑫・⑬で使います）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>【この画面のしくみメモ】</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="28.5" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="39" ht="14.25" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>・送り状番号の登録は「任意」です。入力しなくても「発送済みにする」に進めます。ここは意図的にそうしています。</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="28.5" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="40" ht="14.25" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>・交換の「完了」は必ず人が押します。日数が経っただけでシステムが自動で完了することはありません。</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="41" ht="14.25" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>・完了するとポイントの消費が確定します。取り消せるのは運用者だけです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="28.5" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>・「届いていない」の連絡を受けても、交換の状態は変わりません。提携企業と運用者が実際の配送状況を確認して判断します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="28.5" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>・「対応中」というステータス表示は、発送型の商品では「発送済み」の意味です（ボタンは「発送済みにする」と出ます）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="28.5" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>・「申請者」＝ポイント交換を申請した導入企業の従業員のことです（提携企業側の画面では「申請者」と表記されます）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="28.5" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>・予約型サービスでは、空き枠をコレクレと同期できないため、予約はサロン側のページで完結させます。コレクレは「予約先の案内」と「交換番号（COCR-0001 の形）」での照合だけを担います。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28.5" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>・ホットペッパービューティーのメニュー・クーポン個別のURLは、ログインしていない人や別の人が開くと予約エラーになることがあるため、サロンのトップページURLを設定してもらう運用にしています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="3" t="n"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>【テスト中に困ったら】</t>
         </is>
       </c>
     </row>
     <row r="42" ht="28.5" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>・「届いていない」の連絡を受けても、交換の状態は変わりません。提携企業と運用者が実際の配送状況を確認して判断します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="14.25" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>・「対応中」というステータス表示は、発送型の商品では「発送済み」の意味です（ボタンは「発送済みにする」と出ます）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="14.25" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>・「申請者」＝ポイント交換を申請した導入企業の従業員のことです（提携企業側の画面では「申請者」と表記されます）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28.5" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>・予約型サービスでは、空き枠をコレクレと同期できないため、予約はサロン側のページで完結させます。コレクレは「予約先の案内」と「交換番号（COCR-0001 の形）」での照合だけを担います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28.5" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>・ホットペッパービューティーのメニュー・クーポン個別のURLは、ログインしていない人や別の人が開くと予約エラーになることがあるため、サロンのトップページURLを設定してもらう運用にしています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28.5" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>・一斉メールは宛先ごとに1通ずつ送るため、受け取った人に他社のアドレスは見えません。同じアドレスが複数の宛先に入っていても1通だけ送ります。1回に送れるのは最大300件です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28.5" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>・導入企業の請求金額 ＝ 月額基本料 ＋ 利用人数（有効ユーザー数）× 月額単価 です。月末締め・翌月15日払いで、当月は「見込み」（月末まで利用人数や設定の変更で変わる）、過去月はその月の記録から計算した「確定」です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28.5" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>・会社名・ステータス・プラン・月額基本料・月額単価は、運用者だけが変更できます。管理者の画面からも、API を直接呼んでも変更できない作りです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50"/>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>【テスト中に困ったら】</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28.5" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>無理に進めず、担当者に連絡してください。「期待する結果」と違う場合は、それ自体が報告対象なので、止まって大丈夫です。</t>
         </is>
@@ -778,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3109,17 +3170,1325 @@
       <c r="I67" s="7" t="n"/>
       <c r="J67" s="7" t="n"/>
     </row>
+    <row r="68" ht="15" customHeight="1">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>⑩運用者：提携企業への一斉メール（新機能・実際にメールが送られます）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="59" customHeight="1">
+      <c r="A69" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>⑩運用者：提携企業への一斉メール（新機能・実際にメールが送られます）</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>メニューとダッシュボードから一斉メールの画面を開ける</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>・運用者でログインしている</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>1. 画面上部のメニューを確認する
+2. 「一斉メール」を押す
+3. ダッシュボードに戻り、「提携企業 一斉メール」のカードを押す</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>・メニューに「一斉メール」がある（メニューが1行に収まっている）
+・どちらからでも「提携企業 一斉メール」の画面が開く
+・「1. 送信先を選ぶ」「2. メールを作成する」「プレビュー」「送信履歴」が並んでいる</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+      <c r="I69" s="3" t="n"/>
+      <c r="J69" s="3" t="n"/>
+    </row>
+    <row r="70" ht="116" customHeight="1">
+      <c r="A70" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>⑩運用者：提携企業への一斉メール（新機能・実際にメールが送られます）</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>状態・商品登録状況・名前で提携企業を絞り込める</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>・状態（登録済／申請中／停止中）や商品の登録状況が違う提携企業がいくつかある</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>1. 画面を開いた直後の「状態」の選択を確認する
+2. 「申請中」「停止中」を押して、表示される提携企業を確認する
+3. 「商品登録」を「商品・サービス未登録」「公開中の商品・サービスなし」に切り替える
+4. 検索欄に提携企業名の一部、または提携企業IDを入れる</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>・最初は「登録済」だけが選ばれている
+・押した状態の提携企業が追加で表示される（「却下」は選択肢にない）
+・「商品・サービス未登録」では登録数が 0 の企業だけ、「公開中の商品・サービスなし」では公開中が 0 の企業だけになる（「公開中／登録数」の列で確認）
+・名前・IDの一部で絞り込める。該当なしなら「条件に合う提携企業がありません。」と出る</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+      <c r="I70" s="3" t="n"/>
+      <c r="J70" s="3" t="n"/>
+    </row>
+    <row r="71" ht="130.25" customHeight="1">
+      <c r="A71" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>⑩運用者：提携企業への一斉メール（新機能・実際にメールが送られます）</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>宛先を開いて、ユーザーごとに選べる</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>・宛先が2件以上ある提携企業がある</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>1. 提携企業の行の「宛先」欄（「0 / 3件」のような表示）を押して開く
+2. 宛先を1人だけチェックする
+3. 提携企業の行のチェックボックスと、右上の「◯ 社選択 ／ 宛先 ◯ 件」を確認する
+4. 提携企業の行のチェックボックスを押す
+5. 「すべて開く」「すべて閉じる」を押す</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>・開くと、宛先ごとに氏名・メールアドレス・種類（「ログインユーザー」「招待中（未ログイン）」「申請者」「連絡先アドレス」）が表示される
+・1人だけ選ぶと、提携企業のチェックが「一部選択」（－の表示）になり、件数が「1 / 3件」になる
+・提携企業のチェックを押すと全員が選ばれる。もう一度押すと全員外れる
+・右上の社数・件数が選択に合わせて変わる
+・「すべて開く／閉じる」で表示中の提携企業がまとめて開閉する</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+      <c r="I71" s="3" t="n"/>
+      <c r="J71" s="3" t="n"/>
+    </row>
+    <row r="72" ht="44.75" customHeight="1">
+      <c r="A72" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>⑩運用者：提携企業への一斉メール（新機能・実際にメールが送られます）</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>停止・削除済みのユーザーは宛先に出ない</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>・提携企業のユーザー管理で、停止または削除したユーザーがいる提携企業がある
+（用意できない場合は「-」で構いません）</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>1. その提携企業の宛先を開く</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>・停止・削除済みのユーザーは宛先に表示されない
+・ユーザーと同じアドレスが連絡先メールアドレスにも登録されている場合は、1件にまとまっている（同じアドレスが2回出ない）</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+      <c r="I72" s="3" t="n"/>
+      <c r="J72" s="3" t="n"/>
+    </row>
+    <row r="73" ht="44.75" customHeight="1">
+      <c r="A73" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>⑩運用者：提携企業への一斉メール（新機能・実際にメールが送られます）</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>宛先が1件もない提携企業は選べない</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>・ユーザーも連絡先メールアドレスも無い提携企業がある
+（用意できない場合は「-」で構いません）</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>1. 一覧でその提携企業の行を確認する</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>・「宛先」欄に赤字で「送信先なし」と表示される
+・チェックボックスが押せない</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+      <c r="I73" s="3" t="n"/>
+      <c r="J73" s="3" t="n"/>
+    </row>
+    <row r="74" ht="130.25" customHeight="1">
+      <c r="A74" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>⑩運用者：提携企業への一斉メール（新機能・実際にメールが送られます）</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>差し込み文字とプレビューが正しく表示される</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>・送信先を1件以上選んでいる</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>1. 件名と本文の初期値を確認する
+2. 本文の途中にカーソルを置いて、「差し込み:」の「{{提携企業名}}」「{{担当者名}}」ボタンを押す
+3. 右側の「プレビュー」を確認する</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>・件名は「【コレクレ】」、本文は「{{提携企業名}}」「{{担当者名}} 様」から始まるひな形が最初から入っている
+・ボタンを押すと、カーソルの位置に差し込み文字が入る
+・プレビューでは、選んだ最初の宛先の提携企業名と担当者名に置き換わっている（「「◯◯」の◯◯ 様宛ての場合の表示です。」と出る）
+・本文の末尾に「本メールは、コレクレに提携企業としてご登録いただいている皆様へお送りしています。」、提携企業向け画面の URL、「コレクレ 運営事務局」が自動で付いている</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+      <c r="I74" s="3" t="n"/>
+      <c r="J74" s="3" t="n"/>
+    </row>
+    <row r="75" ht="87.5" customHeight="1">
+      <c r="A75" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>⑩運用者：提携企業への一斉メール（新機能・実際にメールが送られます）</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>件名・本文・送信先が足りないと送れない</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>・一斉メールの画面を開いている</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>1. 件名を空にする
+2. 件名を戻し、本文を空にする
+3. 本文を戻し、送信先をすべて外す
+4. 件名・本文の文字数表示を確認する</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>・それぞれ「件名を入力してください。」「本文を入力してください。」「送信先を選択してください。」と表示される
+・その間は「送信内容を確認する」が押せない（件名・本文が空のときは「自分にテスト送信」も押せない）
+・件名は「◯ / 100」、本文は「◯ / 10000」と文字数が表示され、上限を超えて入力できない</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
+      <c r="I75" s="3" t="n"/>
+      <c r="J75" s="3" t="n"/>
+    </row>
+    <row r="76" ht="101.75" customHeight="1">
+      <c r="A76" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>⑩運用者：提携企業への一斉メール（新機能・実際にメールが送られます）</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>「自分にテスト送信」は自分にだけ届く</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>・テスト用の提携企業を送信先に選んでいる
+・運用者のメールを受信できる</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>1. 件名と本文を入力する
+2. 「自分にテスト送信」を押す
+3. 運用者のメールと、テスト用提携企業のメールを確認する
+4. 画面下の「送信履歴」を確認する</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>・「テストメールを（運用者のアドレス）に送信しました。」と表示される
+・運用者のアドレスにだけ、件名の先頭に「[テスト送信]」が付いたメールが1通届く
+・差し込み文字は、選んだ最初の宛先の内容に置き換わっている
+・提携企業側にはメールが届かない
+・送信履歴には追加されない</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="n"/>
+      <c r="H76" s="3" t="n"/>
+      <c r="I76" s="3" t="n"/>
+      <c r="J76" s="3" t="n"/>
+    </row>
+    <row r="77" ht="101.75" customHeight="1">
+      <c r="A77" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>⑩運用者：提携企業への一斉メール（新機能・実際にメールが送られます）</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>★ 送信前に確認ダイアログが出て、選んだ宛先に送られる</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>・テスト用の提携企業2社を選んでいる（うち1社は宛先の一部だけを選ぶ）</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>1. 「送信内容を確認する」を押す
+2. ダイアログの内容を読む
+3. 「◯件に送信する」を押す
+4. 送信後の画面を確認する</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>・「一斉メールを送信」のダイアログに「送信したメールは取り消せません。内容と送信先をご確認ください。」と出る
+・件名、「送信先: ◯社 ／ ◯件」、提携企業名の一覧が出る。一部だけ選んだ企業は「◯◯（1/3件）」のように件数付きで出る
+・送信すると「◯件のメールを送信しました。」と表示され、送信先の選択がすべて外れる
+・選ばなかった宛先にはメールが届いていない</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+      <c r="I77" s="3" t="n"/>
+      <c r="J77" s="3" t="n"/>
+    </row>
+    <row r="78" ht="116" customHeight="1">
+      <c r="A78" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>⑩運用者：提携企業への一斉メール（新機能・実際にメールが送られます）</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>★ 宛先ごとに1通ずつ届き、他社のアドレスが見えない</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>・上のシナリオで本送信したメールを、2社ぶんのアドレスで受け取っている</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>1. 届いたメールの宛先（To・CC）を確認する
+2. 本文の差し込み部分を確認する
+3. 差出人を確認する</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>・To には自分のアドレスだけが入っている（他社・他の人のアドレスが To・CC に出ていない）
+・「{{提携企業名}}」「{{担当者名}}」が、その宛先の提携企業名・氏名に置き換わっている（連絡先アドレスで登録されていて名前が無い場合は「ご担当者」）
+・差出人がコレクレの送信元アドレスになっている
+※他社のアドレスが見えると情報漏えいになるため、必ず確認してください。</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="n"/>
+      <c r="I78" s="3" t="n"/>
+      <c r="J78" s="3" t="n"/>
+    </row>
+    <row r="79" ht="73.25" customHeight="1">
+      <c r="A79" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>⑩運用者：提携企業への一斉メール（新機能・実際にメールが送られます）</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>送信履歴が残り、内容を再利用できる</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>・本送信を1回以上行っている</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>1. 「送信履歴」の一番上の行を確認する
+2. 行を押して開く
+3. 「この内容を作成欄にコピー」を押す</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>・件名、送信日時、送信した運用者の名前、社数、「送信 ◯ / ◯ 件」が表示される
+・開くと、送信先の提携企業名と本文が表示される（送信に失敗した宛先があれば「送信失敗:」として赤字で出る）
+・コピーすると件名と本文が作成欄に入り、画面の上に戻る</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="3" t="n"/>
+      <c r="I79" s="3" t="n"/>
+      <c r="J79" s="3" t="n"/>
+    </row>
+    <row r="80" ht="87.5" customHeight="1">
+      <c r="A80" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>⑩運用者：提携企業への一斉メール（新機能・実際にメールが送られます）</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>7日以内に送っていると、送りすぎの注意が出る</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>・7日以内に本送信を行っている</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>1. 一斉メールの画面を開き直す
+2. 送信先を選んで「送信内容を確認する」を押す</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>・画面上部に「前回の一斉送信は今日です」（または「◯日前です」）と、前回の日時・件名が黄色で表示される
+・「短い間隔で何度も送ると、迷惑メール扱いや受信拒否につながるおそれがあります。」と出る
+・確認ダイアログにも「送信間隔にご注意ください。」の注意が出る
+※注意だけで、送信は止めません。</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="n"/>
+      <c r="H80" s="3" t="n"/>
+      <c r="I80" s="3" t="n"/>
+      <c r="J80" s="3" t="n"/>
+    </row>
+    <row r="81" ht="15" customHeight="1">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>⑪請求情報：月額基本料と請求管理（新機能）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="116" customHeight="1">
+      <c r="A82" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>⑪請求情報：月額基本料と請求管理（新機能）</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>企業の登録・編集で月額基本料を入力できる</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>・運用者でログインしている</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>1. 企業登録の画面で、新規登録フォームの料金の欄を確認する
+2. 月額基本料を空にする、または「-100」にして登録しようとする
+3. 既存の企業の編集ダイアログを開いて、料金の欄を確認する
+4. 企業一覧のカードを確認する</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>・「月額基本料（円）」の欄が「月額単価（円）」の隣にあり、新規登録では「0」が入っている
+・説明に「利用人数に関係なく毎月かかる基本料です。」と出る
+・空や負の数では「0 以上の整数で入力してください。」と表示され、登録できない
+・編集ダイアログでも月額基本料を変更できる
+・企業一覧のカードに「月額基本料 ◯ 円 / 月額単価 ◯ 円」と表示される</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="n"/>
+      <c r="H82" s="3" t="n"/>
+      <c r="I82" s="3" t="n"/>
+      <c r="J82" s="3" t="n"/>
+    </row>
+    <row r="83" ht="101.75" customHeight="1">
+      <c r="A83" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>⑪請求情報：月額基本料と請求管理（新機能）</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>運用者の「請求管理」画面を開ける</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>・運用者でログインしている</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>1. メニューの「請求管理」を押す
+2. 上部の4つの数字と、「請求対象月」の選択を確認する</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>・「請求管理」の画面が開く
+・「請求対象月」は当月が「（当月）」付きで選ばれている
+・「請求金額合計（見込み）」「請求対象企業 ◯社」「請求日（締め日）」「支払期限」が表示される
+・請求日は当月の末日、支払期限は翌月15日になっている
+・「請求金額 ＝ 月額基本料 ＋ 利用人数（有効ユーザー） × 月額単価。月末締め・翌月 15 日払い。」と説明が出る</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="n"/>
+      <c r="H83" s="3" t="n"/>
+      <c r="I83" s="3" t="n"/>
+      <c r="J83" s="3" t="n"/>
+    </row>
+    <row r="84" ht="73.25" customHeight="1">
+      <c r="A84" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>⑪請求情報：月額基本料と請求管理（新機能）</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>★ 請求金額が「月額基本料＋利用人数×月額単価」になっている</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>・請求確認用の導入企業の、月額基本料・月額単価・有効ユーザー数を控えている</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>1. 請求管理で当月を選ぶ
+2. その企業の行の、利用人数・月額基本料・月額単価・請求金額を確認する
+3. 電卓で「月額基本料＋利用人数×月額単価」を計算して比べる
+4. 表の下の「合計」と、上部の「請求金額合計」を確認する</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>・利用人数・月額基本料・月額単価が控えた値と一致する
+・請求金額が計算結果と一致する
+・当月の行の状態が「見込み」になっている
+・合計が、表示されている企業の請求金額の合計と一致する
+※請求書の金額に直結するため、数字で必ず確認してください。</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="n"/>
+      <c r="H84" s="3" t="n"/>
+      <c r="I84" s="3" t="n"/>
+      <c r="J84" s="3" t="n"/>
+    </row>
+    <row r="85" ht="101.75" customHeight="1">
+      <c r="A85" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>⑪請求情報：月額基本料と請求管理（新機能）</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>利用人数や料金を変えると、当月の見込み額だけが変わる</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>・上のシナリオの企業を使う
+・その企業に過去月の請求がある（状態が「確定」の月がある）</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>1. 管理者の従業員管理で、テスト用の従業員を1人「休止中」にする（または1人追加する）
+2. 運用者の請求管理を開き直し、当月の利用人数と請求金額を確認する
+3. 運用者の企業登録で、月額基本料を変更する
+4. 請求管理を開き直し、当月と過去月の金額を確認する
+5. 変えた値を元に戻す</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>・当月の利用人数と請求金額が、変更に合わせて増減する
+・月額基本料を変えると、当月の請求金額に反映される
+・過去月（「確定」の月）の金額は変わらない
+※月名の横に「※」が付いた月は、当時の記録が無いため現在の設定で計算した参考値です。この月は変わることがあります。</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="n"/>
+      <c r="H85" s="3" t="n"/>
+      <c r="I85" s="3" t="n"/>
+      <c r="J85" s="3" t="n"/>
+    </row>
+    <row r="86" ht="59" customHeight="1">
+      <c r="A86" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>⑪請求情報：月額基本料と請求管理（新機能）</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>無効にした企業は「請求なし」になる</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>・請求確認用の導入企業がある</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>1. 運用者の企業登録で、その企業のステータスを「無効」にする
+2. 請求管理で当月を確認する
+3. ステータスを元に戻す</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>・その企業の状態が「請求なし」になり、下に「無効」と表示される
+・請求金額が ¥0 になる
+・「請求対象企業」の社数と「請求金額合計」から外れる
+・ステータスを戻すと、元の金額に戻る</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="n"/>
+      <c r="H86" s="3" t="n"/>
+      <c r="I86" s="3" t="n"/>
+      <c r="J86" s="3" t="n"/>
+    </row>
+    <row r="87" ht="87.5" customHeight="1">
+      <c r="A87" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>⑪請求情報：月額基本料と請求管理（新機能）</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>企業ごとの請求履歴と、過去月の表示を確認できる</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>・契約開始から2か月以上たっている企業がある</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>1. 請求管理の一覧で企業名を押す
+2. 開いた請求履歴を確認する
+3. 「請求対象月」で前月を選ぶ</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>・その企業の請求履歴が新しい月から順に表示される（契約開始月まで。最大24か月）
+・各月の請求日はその月の末日、支払期限は翌月15日になっている
+・当月は「見込み」、過去月は「確定」と表示される
+・前月を選ぶと、上部の合計が「（見込み）」の付かない「請求金額合計」になり、請求日・支払期限が前月分に変わる</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="n"/>
+      <c r="H87" s="3" t="n"/>
+      <c r="I87" s="3" t="n"/>
+      <c r="J87" s="3" t="n"/>
+    </row>
+    <row r="88" ht="87.5" customHeight="1">
+      <c r="A88" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>⑪請求情報：月額基本料と請求管理（新機能）</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>管理者の各種情報に「請求情報」タブが出る</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>・管理者（導入企業）でログインしている</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>1. 各種情報の画面を開く
+2. 「請求情報」タブを押す
+3. 表示内容を確認する</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>・タブの並びの最後に「請求情報」がある
+・「◯年◯月分のご利用料金（見込み）」と金額、内訳（「月額基本料」と「ID 料金（¥単価 × ◯ 人）」）が出る
+・「請求日（締め日）」と「お支払期限」が出る
+・これまでの請求履歴が表で出る
+・自社の情報だけが表示され、他社の金額は見えない</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="n"/>
+      <c r="H88" s="3" t="n"/>
+      <c r="I88" s="3" t="n"/>
+      <c r="J88" s="3" t="n"/>
+    </row>
+    <row r="89" ht="30.5" customHeight="1">
+      <c r="A89" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>⑪請求情報：月額基本料と請求管理（新機能）</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>★ 管理者と運用者で請求金額が一致する</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>・同じ導入企業について、管理者と運用者の両方で画面を開ける</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>1. 管理者の「請求情報」タブで、当月と前月の請求金額を控える
+2. 運用者の請求管理で、同じ企業の当月と前月の請求金額を確認する</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>・当月・前月とも、金額・利用人数・請求日・支払期限が一致する</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="n"/>
+      <c r="H89" s="3" t="n"/>
+      <c r="I89" s="3" t="n"/>
+      <c r="J89" s="3" t="n"/>
+    </row>
+    <row r="90" ht="59" customHeight="1">
+      <c r="A90" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>⑪請求情報：月額基本料と請求管理（新機能）</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>収支ダッシュボードの収入に月額基本料が含まれる</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>・月額基本料を 0 円より大きくした企業がある</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>1. 運用者の収支ダッシュボード（/finance）を開く
+2. 「当月の収入」の説明文を読む
+3. 企業ごとの収入の表を確認する
+4. 請求管理の当月の「請求金額合計」と比べる</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>・説明が「導入企業の月額基本料 + 従業員数 × 月額単価」になっている
+・企業ごとの表に「月額基本料」の列がある
+・当月の収入が、請求管理の当月の請求金額合計と一致する</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="n"/>
+      <c r="H90" s="3" t="n"/>
+      <c r="I90" s="3" t="n"/>
+      <c r="J90" s="3" t="n"/>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t>⑫提携企業向けの操作ガイド（/docs）（新機能）</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="44.75" customHeight="1">
+      <c r="A92" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>⑫提携企業向けの操作ガイド（/docs）（新機能）</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>ログインしていなくても操作ガイドが開ける</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>・ログインしていない状態のブラウザ（シークレットウィンドウ）を用意する</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>1. 提携企業向け画面の URL の末尾に「/docs」を付けて開く
+2. 画面右上の「ログイン画面へ」を押す</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>・ログイン画面に飛ばされず、「操作ガイド」のトップページ（はじめに）が開く
+・「ログイン画面へ」で提携企業のログイン画面に移る</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="n"/>
+      <c r="H92" s="3" t="n"/>
+      <c r="I92" s="3" t="n"/>
+      <c r="J92" s="3" t="n"/>
+    </row>
+    <row r="93" ht="87.5" customHeight="1">
+      <c r="A93" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>⑫提携企業向けの操作ガイド（/docs）（新機能）</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>目次から各章に移動できる</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>・操作ガイドを開いている（パソコンの画面幅）</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>1. 左側の目次を確認する
+2. 各章を順に開く
+3. ページ下部の「前のページ」「次のページ」で移動する</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>・目次が「はじめる」「毎日の操作」「設定・管理」「困ったとき」に分かれ、全14章ある
+・「収支・精算（請求）」「会社情報の確認・変更」「ユーザーを追加する」に「管理者」の印が付いている
+・どの章も開ける（エラーや真っ白な画面にならない）
+・前後のページ送りで順番どおりに移動できる</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="n"/>
+      <c r="H93" s="3" t="n"/>
+      <c r="I93" s="3" t="n"/>
+      <c r="J93" s="3" t="n"/>
+    </row>
+    <row r="94" ht="44.75" customHeight="1">
+      <c r="A94" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>⑫提携企業向けの操作ガイド（/docs）（新機能）</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>スマートフォンの画面幅でも読める</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>・スマートフォン、またはブラウザの画面幅を狭くできる</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>1. スマートフォンで操作ガイドを開く
+2. 「目次を開く」を押して章を選ぶ
+3. 本文と画像を確認する</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>・左の目次の代わりに「目次を開く」が表示され、そこから章に移動できる
+・文字や画像が画面からはみ出さず、横スクロールしなくても読める</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="n"/>
+      <c r="H94" s="3" t="n"/>
+      <c r="I94" s="3" t="n"/>
+      <c r="J94" s="3" t="n"/>
+    </row>
+    <row r="95" ht="30.5" customHeight="1">
+      <c r="A95" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>⑫提携企業向けの操作ガイド（/docs）（新機能）</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>スクリーンショットがすべて表示される</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>・操作ガイドを開いている</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>1. 全14章を開いて、画像を確認する</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>・画像が欠けている（壊れた画像のマークが出る）ページがない
+・画像の中の赤枠・番号と、本文の手順の番号が合っている</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="n"/>
+      <c r="H95" s="3" t="n"/>
+      <c r="I95" s="3" t="n"/>
+      <c r="J95" s="3" t="n"/>
+    </row>
+    <row r="96" ht="87.5" customHeight="1">
+      <c r="A96" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>⑫提携企業向けの操作ガイド（/docs）（新機能）</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>★ 説明の内容が実際の画面と合っている</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>・提携企業でログインした画面を、別のウィンドウで開いている</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>1. 「交換申請に対応する」「お届け日の調整」「予約が必要なサービス」の章を読む
+2. 書かれている手順どおりに実際の画面を操作してみる</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>・ボタン名・項目名・手順が実際の画面と一致する（例: 「発送済みにする」、送り状番号は任意、希望日の応答は「3 営業日以内」、予約に使っているサービスの選択、ホットペッパーはサロンのトップページURL）
+※今回の①〜⑨の変更が説明に反映されているかの確認です。違う箇所があれば、章の名前と一緒に気づきリストに書いてください。</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="n"/>
+      <c r="H96" s="3" t="n"/>
+      <c r="I96" s="3" t="n"/>
+      <c r="J96" s="3" t="n"/>
+    </row>
+    <row r="97" ht="15" customHeight="1">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t>⑬セキュリティ修正（管理者の会社情報・運用者のログイン必須化）</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="87.5" customHeight="1">
+      <c r="A98" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>⑬セキュリティ修正（管理者の会社情報・運用者のログイン必須化）</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>管理者の会社情報で、会社名などの契約項目は変えられない</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>・管理者（導入企業）でログインしている</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>1. 各種情報の「会社情報」タブを開く
+2. 会社名の欄を確認する
+3. 住所や担当者名を変更して「会社情報を保存」を押す
+4. 運用者の企業登録で、その企業の会社名・ステータス・プラン・月額基本料・月額単価を確認する</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>・説明に「会社名は変更できません。」とあり、会社名は編集できない
+・住所・担当者名などは保存でき、「各種情報を更新しました」と表示される
+・運用者側で見た会社名・ステータス・プラン・料金は、保存前と変わっていない</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="n"/>
+      <c r="H98" s="3" t="n"/>
+      <c r="I98" s="3" t="n"/>
+      <c r="J98" s="3" t="n"/>
+    </row>
+    <row r="99" ht="59" customHeight="1">
+      <c r="A99" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>⑬セキュリティ修正（管理者の会社情報・運用者のログイン必須化）</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>理念体系の保存はこれまでどおりできる</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>・管理者（導入企業）でログインしている</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>1. 各種情報の「理念体系」タブで、項目を1つ変更する
+2. 「理念体系を保存」を押す
+3. 画面を開き直す</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>・「理念体系を更新しました」と表示される
+・開き直しても変更が残っている
+※今回の修正で、管理者が保存できる契約系の項目は理念体系だけになりました。巻き添えで保存できなくなっていないかの確認です。</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="n"/>
+      <c r="H99" s="3" t="n"/>
+      <c r="I99" s="3" t="n"/>
+      <c r="J99" s="3" t="n"/>
+    </row>
+    <row r="100" ht="101.75" customHeight="1">
+      <c r="A100" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>⑬セキュリティ修正（管理者の会社情報・運用者のログイン必須化）</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>API を直接呼んでも月額単価などを書き換えられない</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>・管理者（導入企業）でログインしている
+・ブラウザの開発者ツールを使える
+（開発者向けの確認です。難しい場合は「-」で構いません）</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>1. 管理者画面で開発者ツールのコンソールを開く
+2. 次を実行する
+fetch('/api/company-info',{method:'PATCH',headers:{'Content-Type':'application/json'},body:JSON.stringify({name:'改ざんテスト',status:'INACTIVE',plan:'TRIAL',monthlyBaseFee:0,perEmployeeMonthlyFee:1,pointUnitLabel:'x'})}).then(r=&gt;r.status)
+3. 運用者の企業登録と請求管理で、その企業を確認する</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>・会社名・ステータス・プラン・月額基本料・月額単価・ポイント単位がどれも変わっていない
+・請求管理の金額も変わっていない
+※修正前は、この方法で自社の月額単価を書き換えて請求額を下げられる状態でした。</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="n"/>
+      <c r="H100" s="3" t="n"/>
+      <c r="I100" s="3" t="n"/>
+      <c r="J100" s="3" t="n"/>
+    </row>
+    <row r="101" ht="44.75" customHeight="1">
+      <c r="A101" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>⑬セキュリティ修正（管理者の会社情報・運用者のログイン必須化）</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>ログインしていないと、運用者の各画面はログイン画面に移る</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>・ログインしていない状態のブラウザ（シークレットウィンドウ）を用意する</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>1. 運用者画面の URL の末尾に「/finance」を付けて開く
+2. ログインする
+3. 同じように「/billing」「/merchant-broadcast」も開いてみる</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>・どれもログイン画面に移り、中身は表示されない
+・ログインすると、開こうとしていた画面（収支ダッシュボードなど）に移る</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="n"/>
+      <c r="H101" s="3" t="n"/>
+      <c r="I101" s="3" t="n"/>
+      <c r="J101" s="3" t="n"/>
+    </row>
+    <row r="102" ht="15" customHeight="1">
+      <c r="A102" s="12" t="inlineStr">
+        <is>
+          <t>⑭開発者向け：本番ビルドの環境変数チェックと CI（テスト担当は「-」で可）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="73.25" customHeight="1">
+      <c r="A103" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>⑭開発者向け：本番ビルドの環境変数チェックと CI（テスト担当は「-」で可）</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>stage のビルドで必須環境変数の不足の警告が出ていない</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>・Vercel の stage（Preview）のデプロイ結果を見られる</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>1. admin・employee・merchant・operator の4アプリそれぞれで、stage の最新デプロイのビルドログを開く
+2. 「[required-env]」で検索する</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>・「[required-env] ◯◯ アプリの preview 環境に、次の環境変数が設定されていません」という警告が出ていない
+・出ている場合は、Vercel の Environment Variables に足りない変数を設定する
+※Preview では警告だけで、ビルドは止まりません。</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="n"/>
+      <c r="H103" s="3" t="n"/>
+      <c r="I103" s="3" t="n"/>
+      <c r="J103" s="3" t="n"/>
+    </row>
+    <row r="104" ht="87.5" customHeight="1">
+      <c r="A104" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>⑭開発者向け：本番ビルドの環境変数チェックと CI（テスト担当は「-」で可）</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>★ 本番の環境変数がそろっていることを main マージ前に確認する</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>・Vercel の Production の環境変数を見られる</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>1. 各アプリの README の「本番で必須の環境変数」の表を開く
+2. Vercel の4アプリそれぞれで、Production の Environment Variables と照らし合わせる</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>・表にある環境変数が、4アプリすべての Production に設定されている（特に operator の CRON_SECRET、各アプリの AWS_ROLE_ARN・*_APP_URL）
+※足りないまま main にマージすると、本番のビルドが失敗してデプロイされません（稼働中の本番は前のまま動き続けます）。マージ後にビルドが失敗したら、ログに不足している変数名が出ます。</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="n"/>
+      <c r="H104" s="3" t="n"/>
+      <c r="I104" s="3" t="n"/>
+      <c r="J104" s="3" t="n"/>
+    </row>
+    <row r="105" ht="44.75" customHeight="1">
+      <c r="A105" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>⑭開発者向け：本番ビルドの環境変数チェックと CI（テスト担当は「-」で可）</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>CI（lint・ユニットテスト・統合テスト）が通っている</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>・GitHub の Actions を見られる</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>1. stage の最新のコミット、または main への Pull Request の Checks を開く
+2. 「CI」ワークフローの各ジョブを確認する</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>・「Lint」「Test」（ユニットテスト）「Integration (DynamoDB Local)」（統合テスト）がすべて成功している</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="n"/>
+      <c r="H105" s="3" t="n"/>
+      <c r="I105" s="3" t="n"/>
+      <c r="J105" s="3" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="14">
     <mergeCell ref="A47:J47"/>
+    <mergeCell ref="A102:J102"/>
     <mergeCell ref="A32:J32"/>
     <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A97:J97"/>
     <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A91:J91"/>
     <mergeCell ref="A55:J55"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A38:J38"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A81:J81"/>
     <mergeCell ref="A42:J42"/>
+    <mergeCell ref="A68:J68"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
